--- a/Daftar/Data2.xlsx
+++ b/Daftar/Data2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T490S\Documents\Website-Pertama\Bendahara_Kelas\Daftar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDEDFF4-2CED-497D-BD08-9114EF5859B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB3A677-9377-445F-9EE6-158E569719BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{EC21BC5C-CE14-4CB3-A04A-DABB43A64A1E}"/>
   </bookViews>
@@ -1661,112 +1661,304 @@
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1"/>
-      <c r="W12" s="1"/>
-      <c r="X12" s="1"/>
-      <c r="Y12" s="1"/>
-      <c r="Z12" s="1"/>
-      <c r="AA12" s="1"/>
-      <c r="AB12" s="1"/>
-      <c r="AC12" s="1"/>
-      <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
-      <c r="AF12" s="1"/>
-      <c r="AG12" s="1"/>
+      <c r="B12" s="1">
+        <v>26000</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>16000</v>
+      </c>
+      <c r="E12" s="1">
+        <v>15000</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G12" s="1">
+        <v>31000</v>
+      </c>
+      <c r="H12" s="1">
+        <v>19000</v>
+      </c>
+      <c r="I12" s="1">
+        <v>21000</v>
+      </c>
+      <c r="J12" s="1">
+        <v>6000</v>
+      </c>
+      <c r="K12" s="1">
+        <v>6000</v>
+      </c>
+      <c r="L12" s="1">
+        <v>16000</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>46000</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>37000</v>
+      </c>
+      <c r="S12" s="1">
+        <v>16000</v>
+      </c>
+      <c r="T12" s="1">
+        <v>26000</v>
+      </c>
+      <c r="U12" s="1">
+        <v>11000</v>
+      </c>
+      <c r="V12" s="1">
+        <v>18000</v>
+      </c>
+      <c r="W12" s="1">
+        <v>9000</v>
+      </c>
+      <c r="X12" s="1">
+        <v>22000</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>16000</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>10000</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>39000</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>31000</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>35000</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="1">
+        <v>10000</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>34000</v>
+      </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="1"/>
-      <c r="W13" s="1"/>
-      <c r="X13" s="1"/>
-      <c r="Y13" s="1"/>
-      <c r="Z13" s="1"/>
-      <c r="AA13" s="1"/>
-      <c r="AB13" s="1"/>
-      <c r="AC13" s="1"/>
-      <c r="AD13" s="1"/>
-      <c r="AE13" s="1"/>
-      <c r="AF13" s="1"/>
-      <c r="AG13" s="1"/>
+      <c r="B13" s="1">
+        <v>26000</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1">
+        <v>16000</v>
+      </c>
+      <c r="E13" s="1">
+        <v>15000</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G13" s="1">
+        <v>31000</v>
+      </c>
+      <c r="H13" s="1">
+        <v>19000</v>
+      </c>
+      <c r="I13" s="1">
+        <v>21000</v>
+      </c>
+      <c r="J13" s="1">
+        <v>6000</v>
+      </c>
+      <c r="K13" s="1">
+        <v>6000</v>
+      </c>
+      <c r="L13" s="1">
+        <v>16000</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>46000</v>
+      </c>
+      <c r="O13" s="1">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1">
+        <v>37000</v>
+      </c>
+      <c r="S13" s="1">
+        <v>16000</v>
+      </c>
+      <c r="T13" s="1">
+        <v>26000</v>
+      </c>
+      <c r="U13" s="1">
+        <v>11000</v>
+      </c>
+      <c r="V13" s="1">
+        <v>18000</v>
+      </c>
+      <c r="W13" s="1">
+        <v>9000</v>
+      </c>
+      <c r="X13" s="1">
+        <v>22000</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>16000</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>10000</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>39000</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>31000</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>35000</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="1">
+        <v>10000</v>
+      </c>
+      <c r="AG13" s="1">
+        <v>34000</v>
+      </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-      <c r="Z14" s="1"/>
-      <c r="AA14" s="1"/>
-      <c r="AB14" s="1"/>
-      <c r="AC14" s="1"/>
-      <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
-      <c r="AF14" s="1"/>
-      <c r="AG14" s="1"/>
+      <c r="B14" s="1">
+        <v>26000</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>16000</v>
+      </c>
+      <c r="E14" s="1">
+        <v>15000</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G14" s="1">
+        <v>31000</v>
+      </c>
+      <c r="H14" s="1">
+        <v>19000</v>
+      </c>
+      <c r="I14" s="1">
+        <v>21000</v>
+      </c>
+      <c r="J14" s="1">
+        <v>6000</v>
+      </c>
+      <c r="K14" s="1">
+        <v>6000</v>
+      </c>
+      <c r="L14" s="1">
+        <v>16000</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>46000</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <v>37000</v>
+      </c>
+      <c r="S14" s="1">
+        <v>16000</v>
+      </c>
+      <c r="T14" s="1">
+        <v>26000</v>
+      </c>
+      <c r="U14" s="1">
+        <v>11000</v>
+      </c>
+      <c r="V14" s="1">
+        <v>18000</v>
+      </c>
+      <c r="W14" s="1">
+        <v>9000</v>
+      </c>
+      <c r="X14" s="1">
+        <v>22000</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>16000</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>10000</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>39000</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>31000</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>35000</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="1">
+        <v>10000</v>
+      </c>
+      <c r="AG14" s="1">
+        <v>34000</v>
+      </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
